--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (CV on 29 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (CV on 13 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (CV on all 50 ref sites)</t>
+          <t>Baseline (CV on all 42 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>406</v>
+        <v>278</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (CV on 13 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (CV on 27 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (CV on all 42 ref sites)</t>
+          <t>Baseline (CV on all 59 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>143</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>278</v>
+        <v>545</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (CV on 27 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (CV on 16 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (CV on all 59 ref sites)</t>
+          <t>Baseline (CV on all 52 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C12" t="n">
-        <v>545</v>
+        <v>414</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cv_confusion.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (CV on 16 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (CV on 17 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (CV on all 52 ref sites)</t>
+          <t>Baseline (CV on all 59 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>414</v>
+        <v>545</v>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
